--- a/20240403_Er_test/output/20240403_Er_test_site_pairs.xlsx
+++ b/20240403_Er_test/output/20240403_Er_test_site_pairs.xlsx
@@ -10,9 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ga" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ni" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-In" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
@@ -740,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -767,11 +767,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.055</v>
+        <v>3.009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -791,46 +791,31 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.294</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.104</v>
+      </c>
       <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.183</v>
+        <v>0.135</v>
       </c>
       <c r="C6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -914,7 +899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -941,11 +926,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.009</v>
+        <v>3.055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -965,31 +950,46 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.294</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3.104</v>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.183</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
